--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126780230</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>126780266</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>126780436</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>126780328</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>126780302</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126780230</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>126780266</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>126780436</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>126780328</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>126780302</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1368,6 +1368,436 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127373198</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97320</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 33691, Hultserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>571016</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6400584</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ann Newsome, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127373177</v>
+      </c>
+      <c r="B9" t="n">
+        <v>105477</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 33691, Hultserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>570979</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6400549</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ann Newsome, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127372958</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 33691, Hultserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>571026</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6400197</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ann Newsome, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127372980</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58027</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 33691, Hultserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>571026</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6400197</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ann Newsome, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126780230</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>126780266</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>126780436</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>126780328</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>126780302</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>127373198</v>
       </c>
       <c r="B8" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>127373177</v>
       </c>
       <c r="B9" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126780230</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>126780481</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>126780266</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>126780436</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>126780328</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>126780302</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>127373198</v>
       </c>
       <c r="B8" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>127373177</v>
       </c>
       <c r="B9" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127372958</v>
       </c>
       <c r="B10" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127372980</v>
       </c>
       <c r="B11" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -1475,7 +1475,7 @@
         <v>127373177</v>
       </c>
       <c r="B9" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -1373,7 +1373,7 @@
         <v>127373198</v>
       </c>
       <c r="B8" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>127373177</v>
       </c>
       <c r="B9" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127372958</v>
       </c>
       <c r="B10" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127372980</v>
       </c>
       <c r="B11" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ann Newsome, Sven Halling</t>
+          <t>Sven Halling, Ann Newsome, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -1373,7 +1373,7 @@
         <v>127373198</v>
       </c>
       <c r="B8" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ann Newsome, Sven Halling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1475,7 +1475,7 @@
         <v>127373177</v>
       </c>
       <c r="B9" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -1373,7 +1373,7 @@
         <v>127373198</v>
       </c>
       <c r="B8" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>127373177</v>
       </c>
       <c r="B9" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127372958</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127372980</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -1373,7 +1373,7 @@
         <v>127373198</v>
       </c>
       <c r="B8" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>127373177</v>
       </c>
       <c r="B9" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127372958</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127372980</v>
       </c>
       <c r="B11" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -1373,7 +1373,7 @@
         <v>127373198</v>
       </c>
       <c r="B8" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>127373177</v>
       </c>
       <c r="B9" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ann Newsome, Sven Halling</t>
+          <t>Sven Halling, Ann Newsome, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ann Newsome, Sven Halling</t>
+          <t>Sven Halling, Ann Newsome, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 33691-2025 artfynd.xlsx
+++ b/artfynd/A 33691-2025 artfynd.xlsx
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ann Newsome, Sven Halling</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ann Newsome, Sven Halling</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
